--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_rf_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_rf_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>40391.3308121194</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>20045.5039848095</v>
+        <v>69260.1092327274</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>38923.1469224532</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>18954.3403234552</v>
+        <v>65517.2558935058</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>36755.9239777296</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>17356.8598193119</v>
+        <v>59374.321847234</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>35458.7846707646</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>16408.8205168213</v>
+        <v>55665.5304894489</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>32866.8338060242</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>14534.3697432646</v>
+        <v>49563.377940023</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>31663.4909783065</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>13673.9399966553</v>
+        <v>45978.9667341839</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>31089.9619245182</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>13266.2030421381</v>
+        <v>44706.3295560828</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>30439.8010676965</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>12805.9059163448</v>
+        <v>43268.4276302563</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>29919.5385012173</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>12439.0898979456</v>
+        <v>42003.0037836725</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>28633.7528020638</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>11538.5909653134</v>
+        <v>38506.6549498762</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>27745.3434195867</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>11228.7913153586</v>
+        <v>35767.8088914174</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>26411.6512455682</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>11270.7528952336</v>
+        <v>32257.0765324382</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>25582.0365599528</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>11290.9006146716</v>
+        <v>30124.4464643159</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>25121.1925286227</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>11300.0035872191</v>
+        <v>29254.437032879</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>24332.6254098559</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>10708.6758894762</v>
+        <v>27826.4485242461</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>22374.1669829734</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>8965.35394164674</v>
+        <v>23900.3151473573</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>21736.2162259883</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>8406.02958428872</v>
+        <v>22486.0472157517</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>20821.3275090914</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>7611.936961686</v>
+        <v>20166.168480561</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>19940.6537010291</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>6857.11932469177</v>
+        <v>18286.0449251359</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>19245.1004185654</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>6268.10832976884</v>
+        <v>17103.1106136093</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>18390.63156681</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>5553.82076291486</v>
+        <v>14968.067061991</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>17653.4465890975</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>4946.44450327191</v>
+        <v>13845.065443214</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>16679.6489454913</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>4157.86762678776</v>
+        <v>12290.4578670466</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>15458.9385058532</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>2831.01251769887</v>
+        <v>8685.37648345189</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>15162.5766301147</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>1921.74483542696</v>
+        <v>8422.3943287044</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>13780.9302009256</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>2193.75065379212</v>
+        <v>6561.28145373777</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>13443.3439630725</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>3165.45301172993</v>
+        <v>6281.56314115373</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>13110.1323166132</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>4110.20475216059</v>
+        <v>6494.06592704237</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>12211.4834574472</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>6581.04602774748</v>
+        <v>6575.74203285711</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>11699.1211008173</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>7934.46793679625</v>
+        <v>7018.47630141369</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>11302.7242250858</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>8951.01589254245</v>
+        <v>7613.6480054603</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>10267.3527914016</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>10251.0971723825</v>
+        <v>9222.95546517866</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>9793.34846637782</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>10138.4001800959</v>
+        <v>9644.00387414394</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>9046.72247638972</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>10099.9413430911</v>
+        <v>9548.46289124855</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>8513.07644655899</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>10138.9469442927</v>
+        <v>10082.6491414901</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>8192.57302595514</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>10145.9038377967</v>
+        <v>9901.61672012851</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>7703.89645024796</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>10129.3219579467</v>
+        <v>10248.7012948833</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>5910.23242099075</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>9677.66457037655</v>
+        <v>10326.48944166</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>5606.6154582202</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>9512.51409573541</v>
+        <v>10248.9196992116</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>5429.74007140621</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>9398.87959518086</v>
+        <v>10200.3311130581</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>4514.22008062694</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>8514.87430184238</v>
+        <v>9264.87991205439</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>4206.42781031504</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>8101.22729884184</v>
+        <v>8759.0612089256</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>3978.63649766775</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>7794.23808965123</v>
+        <v>8421.75057729448</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>3355.01101163897</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>6949.72506414673</v>
+        <v>7494.12622557746</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>3212.40438211201</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>6755.7027631857</v>
+        <v>7281.07627898172</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>2613.56599935686</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>5936.83889530426</v>
+        <v>6384.88295383064</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>2518.64725318743</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>5806.38709196962</v>
+        <v>6275.83220036918</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>2145.65616928687</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>5291.83936173004</v>
+        <v>5794.80653565511</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>2076.28649986566</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>5195.78544449434</v>
+        <v>5716.23250661681</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>1858.47889048684</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>4893.41518567132</v>
+        <v>5480.87827190745</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>1569.72440684957</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>4490.61333723629</v>
+        <v>5191.05954378642</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>1088.1715803625</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>3925.13805458706</v>
+        <v>4849.45599530643</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>941.090548307544</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>3758.01292118878</v>
+        <v>4620.25970838142</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>362.99227807021</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>3089.12279674255</v>
+        <v>3806.46869446616</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>189.133021831482</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>2883.67385034536</v>
+        <v>3629.16500776663</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>-45.7347161596536</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>2602.44256943954</v>
+        <v>3425.56748362414</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>-365.236168645591</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>2212.08927362467</v>
+        <v>2995.22534150442</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>-691.405557027065</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>1802.52034434882</v>
+        <v>2361.9495928856</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>-948.034846166367</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>1470.61083395806</v>
+        <v>1962.23714585254</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>-1114.92972269356</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>1249.21748615161</v>
+        <v>1690.61718924797</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>-1277.85296588331</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>1028.0900897203</v>
+        <v>1486.31469667043</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>-1337.78049913942</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>945.343758668958</v>
+        <v>1518.74933332249</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>-1403.80765275918</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>853.204615355606</v>
+        <v>1520.56130009465</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>-1441.09845591437</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>800.688587316306</v>
+        <v>1503.1989259751</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>-1974.86864494059</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>830.548861740726</v>
+        <v>1381.09434853087</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>-2097.57419679803</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>703.909943921291</v>
+        <v>1439.88283727456</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>-2212.12147342183</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>301.167897021436</v>
+        <v>1634.84906150831</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>-2351.35355448941</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>484.270349634453</v>
+        <v>1834.07201625829</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>-2414.70720561001</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>791.310172406429</v>
+        <v>1931.18175638753</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>-2488.61713080216</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>1181.52759442792</v>
+        <v>2138.6306447441</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>-2534.43998421085</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>1444.10228210755</v>
+        <v>2264.24381170198</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>-2607.26672947697</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>1702.70789621668</v>
+        <v>2438.60743572187</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>-2658.78463215654</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>1930.08257263468</v>
+        <v>2544.2022091296</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>-2709.49569447654</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>2536.66534439924</v>
+        <v>2977.95053915036</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>-2687.84647257282</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>2698.99174125161</v>
+        <v>3102.09525841978</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>-2560.6850389912</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>2790.76424895938</v>
+        <v>3268.05443628886</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>-2234.16144081315</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>2725.19593600652</v>
+        <v>3506.89005416467</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>-2025.9792072164</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>2626.37287310903</v>
+        <v>3521.69485954164</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>-1545.61706379204</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>2593.20758371909</v>
+        <v>3571.79971719081</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>-479.825820346973</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>2418.13374396678</v>
+        <v>3727.69340018231</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>-109.384775395015</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>2320.22879928278</v>
+        <v>3675.77226137835</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>481.967730705183</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>2139.32072123979</v>
+        <v>3529.35021303114</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>1728.73669486261</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>2067.51640748037</v>
+        <v>2882.05686671387</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>2642.03989968031</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>2533.57989656313</v>
+        <v>3035.35729638703</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>4556.79651952958</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>3210.71458807037</v>
+        <v>3529.92210185416</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>6366.8204890106</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>3389.67948054511</v>
+        <v>4606.77510808041</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>9012.67758416094</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>1894.67125591655</v>
+        <v>6383.31877552823</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>14038.4729572557</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>3583.95422471394</v>
+        <v>10166.1842561497</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>20158.9565292825</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>9326.44113432619</v>
+        <v>14994.1334981689</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>30650.4786865691</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>19918.4570326093</v>
+        <v>24367.1872225389</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>6.65329130883922</v>
+        <v>2.30793476979226</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
